--- a/graficos/NMF_mejores_dominio.xlsx
+++ b/graficos/NMF_mejores_dominio.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="42">
   <si>
     <t>subconjunto</t>
   </si>
@@ -58,91 +58,85 @@
     <t>orps_lim_dictamen_dom_K35_6</t>
   </si>
   <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>orps_lim_dictamen_dom_K24_2</t>
-  </si>
-  <si>
     <t>todos</t>
   </si>
   <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>todos_dictamen_dom_K26_4</t>
+  </si>
+  <si>
     <t>5</t>
   </si>
   <si>
     <t>todos_dictamen_dom_K26_5</t>
   </si>
   <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>todos_dictamen_dom_K27_7</t>
+  </si>
+  <si>
     <t>1</t>
   </si>
   <si>
-    <t>todos_dictamen_dom_K26_1</t>
-  </si>
-  <si>
-    <t>7</t>
-  </si>
-  <si>
-    <t>todos_dictamen_dom_K25_7</t>
+    <t>todos_dictamen_dom_K31_1</t>
+  </si>
+  <si>
+    <t>todos_dictamen_dom_K32_1</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>todos_dictamen_dom_K29_3</t>
+  </si>
+  <si>
+    <t>todos_dictamen_dom_K27_3</t>
+  </si>
+  <si>
+    <t>todos_dictamen_dom_K35_5</t>
+  </si>
+  <si>
+    <t>orps_lim_dictamen_dom_K30_4</t>
   </si>
   <si>
     <t>comisión</t>
   </si>
   <si>
-    <t>comisión_dictamen_dom_K26_2</t>
-  </si>
-  <si>
-    <t>todos_dictamen_dom_K29_5</t>
-  </si>
-  <si>
-    <t>todos_dictamen_dom_K31_1</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>todos_dictamen_dom_K34_4</t>
-  </si>
-  <si>
-    <t>comisión_lim</t>
-  </si>
-  <si>
-    <t>comisión_lim_dictamen_dom_K35_6</t>
-  </si>
-  <si>
-    <t>todos_dictamen_dom_K29_7</t>
-  </si>
-  <si>
-    <t>orps_lim_dictamen_dom_K32_1</t>
-  </si>
-  <si>
-    <t>orps_lim_dictamen_dom_K30_6</t>
-  </si>
-  <si>
-    <t>todos_dictamen_dom_K34_1</t>
+    <t>comisión_dictamen_dom_K34_5</t>
+  </si>
+  <si>
+    <t>todos_dictamen_dom_K33_1</t>
+  </si>
+  <si>
+    <t>orps</t>
+  </si>
+  <si>
+    <t>orps_dictamen_dom_K35_5</t>
+  </si>
+  <si>
+    <t>todos_dictamen_dom_K34_7</t>
   </si>
   <si>
     <t>8</t>
   </si>
   <si>
-    <t>todos_dictamen_dom_K32_8</t>
-  </si>
-  <si>
-    <t>todos_dictamen_dom_K35_7</t>
-  </si>
-  <si>
-    <t>todos_dictamen_dom_K35_8</t>
-  </si>
-  <si>
-    <t>orps</t>
-  </si>
-  <si>
-    <t>orps_dictamen_dom_K35_7</t>
+    <t>todos_dictamen_dom_K33_8</t>
+  </si>
+  <si>
+    <t>orps_dictamen_dom_K34_8</t>
   </si>
   <si>
     <t>comisión_dictamen_dom_K35_7</t>
   </si>
   <si>
-    <t>3</t>
+    <t>todos_dictamen_dom_K35_3</t>
+  </si>
+  <si>
+    <t>orps_dictamen_dom_K33_3</t>
   </si>
   <si>
     <t>comisión_dictamen_dom_K33_3</t>
@@ -586,39 +580,39 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" s="1" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C3" s="2">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F3" s="3">
-        <v>0.6125</v>
+        <v>0.6</v>
       </c>
       <c r="G3" s="3">
-        <v>-3.054901376456616</v>
+        <v>-2.482147434032872</v>
       </c>
       <c r="H3" s="2">
         <v>16</v>
       </c>
       <c r="I3" s="2">
-        <v>181</v>
+        <v>196</v>
       </c>
       <c r="J3" s="3">
-        <v>0.08839779005524862</v>
+        <v>0.08163265306122448</v>
       </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>11</v>
@@ -650,13 +644,13 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C5" s="2">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D5" s="1" t="s">
         <v>19</v>
@@ -665,30 +659,30 @@
         <v>20</v>
       </c>
       <c r="F5" s="3">
-        <v>0.5884615384615385</v>
+        <v>0.5407407407407407</v>
       </c>
       <c r="G5" s="3">
-        <v>-1.65181718937794</v>
+        <v>-1.431787172266971</v>
       </c>
       <c r="H5" s="2">
         <v>16</v>
       </c>
       <c r="I5" s="2">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="J5" s="3">
-        <v>0.08163265306122448</v>
+        <v>0.08205128205128205</v>
       </c>
     </row>
     <row r="6" spans="1:10">
       <c r="A6" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C6" s="2">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="D6" s="1" t="s">
         <v>21</v>
@@ -697,56 +691,56 @@
         <v>22</v>
       </c>
       <c r="F6" s="3">
-        <v>0.588</v>
+        <v>0.5387096774193548</v>
       </c>
       <c r="G6" s="3">
-        <v>-1.570914823653891</v>
+        <v>-1.627549743466289</v>
       </c>
       <c r="H6" s="2">
         <v>16</v>
       </c>
       <c r="I6" s="2">
-        <v>186</v>
+        <v>222</v>
       </c>
       <c r="J6" s="3">
-        <v>0.08602150537634409</v>
+        <v>0.07207207207207207</v>
       </c>
     </row>
     <row r="7" spans="1:10">
       <c r="A7" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C7" s="2">
+        <v>32</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E7" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="B7" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C7" s="2">
-        <v>26</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>24</v>
-      </c>
       <c r="F7" s="3">
-        <v>0.5653846153846154</v>
+        <v>0.5375</v>
       </c>
       <c r="G7" s="3">
-        <v>-2.772693449325919</v>
+        <v>-1.615539289800598</v>
       </c>
       <c r="H7" s="2">
         <v>16</v>
       </c>
       <c r="I7" s="2">
-        <v>186</v>
+        <v>228</v>
       </c>
       <c r="J7" s="3">
-        <v>0.08602150537634409</v>
+        <v>0.07017543859649122</v>
       </c>
     </row>
     <row r="8" spans="1:10">
       <c r="A8" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>11</v>
@@ -755,222 +749,222 @@
         <v>29</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="E8" s="1" t="s">
         <v>25</v>
       </c>
       <c r="F8" s="3">
-        <v>0.5551724137931034</v>
+        <v>0.5172413793103449</v>
       </c>
       <c r="G8" s="3">
-        <v>-1.626052829081662</v>
+        <v>-1.518542103928442</v>
       </c>
       <c r="H8" s="2">
         <v>16</v>
       </c>
       <c r="I8" s="2">
-        <v>208</v>
+        <v>203</v>
       </c>
       <c r="J8" s="3">
-        <v>0.07692307692307693</v>
+        <v>0.07881773399014778</v>
       </c>
     </row>
     <row r="9" spans="1:10">
       <c r="A9" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C9" s="2">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="E9" s="1" t="s">
         <v>26</v>
       </c>
       <c r="F9" s="3">
-        <v>0.5387096774193548</v>
+        <v>0.5111111111111111</v>
       </c>
       <c r="G9" s="3">
-        <v>-1.627549743466289</v>
+        <v>-1.373895518843885</v>
       </c>
       <c r="H9" s="2">
         <v>16</v>
       </c>
       <c r="I9" s="2">
-        <v>222</v>
+        <v>188</v>
       </c>
       <c r="J9" s="3">
-        <v>0.07207207207207207</v>
+        <v>0.0851063829787234</v>
       </c>
     </row>
     <row r="10" spans="1:10">
       <c r="A10" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C10" s="2">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D10" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E10" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="E10" s="1" t="s">
-        <v>28</v>
-      </c>
       <c r="F10" s="3">
-        <v>0.5264705882352941</v>
+        <v>0.4828571428571429</v>
       </c>
       <c r="G10" s="3">
-        <v>-2.397608592770194</v>
+        <v>-1.766883925881679</v>
       </c>
       <c r="H10" s="2">
         <v>16</v>
       </c>
       <c r="I10" s="2">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="J10" s="3">
-        <v>0.06808510638297872</v>
+        <v>0.06722689075630252</v>
       </c>
     </row>
     <row r="11" spans="1:10">
       <c r="A11" s="1" t="s">
-        <v>29</v>
+        <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C11" s="2">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="F11" s="3">
-        <v>0.5114285714285715</v>
+        <v>0.48</v>
       </c>
       <c r="G11" s="3">
-        <v>-2.000630496581451</v>
+        <v>-2.130146944197147</v>
       </c>
       <c r="H11" s="2">
         <v>16</v>
       </c>
       <c r="I11" s="2">
-        <v>243</v>
+        <v>198</v>
       </c>
       <c r="J11" s="3">
-        <v>0.06584362139917696</v>
+        <v>0.08080808080808081</v>
       </c>
     </row>
     <row r="12" spans="1:10">
       <c r="A12" s="1" t="s">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C12" s="2">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F12" s="3">
-        <v>0.5103448275862069</v>
+        <v>0.4735294117647059</v>
       </c>
       <c r="G12" s="3">
-        <v>-1.982304031232157</v>
+        <v>-2.212744072669193</v>
       </c>
       <c r="H12" s="2">
         <v>16</v>
       </c>
       <c r="I12" s="2">
-        <v>201</v>
+        <v>229</v>
       </c>
       <c r="J12" s="3">
-        <v>0.07960199004975124</v>
+        <v>0.06986899563318777</v>
       </c>
     </row>
     <row r="13" spans="1:10">
       <c r="A13" s="1" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C13" s="2">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F13" s="3">
-        <v>0.490625</v>
+        <v>0.4727272727272727</v>
       </c>
       <c r="G13" s="3">
-        <v>-2.461448013849468</v>
+        <v>-1.686694232866715</v>
       </c>
       <c r="H13" s="2">
         <v>16</v>
       </c>
       <c r="I13" s="2">
-        <v>217</v>
+        <v>223</v>
       </c>
       <c r="J13" s="3">
-        <v>0.07373271889400922</v>
+        <v>0.07174887892376682</v>
       </c>
     </row>
     <row r="14" spans="1:10">
       <c r="A14" s="1" t="s">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C14" s="2">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="E14" s="1" t="s">
         <v>33</v>
       </c>
       <c r="F14" s="3">
-        <v>0.49</v>
+        <v>0.4685714285714286</v>
       </c>
       <c r="G14" s="3">
-        <v>-2.764832251441604</v>
+        <v>-2.315113163115361</v>
       </c>
       <c r="H14" s="2">
         <v>16</v>
       </c>
       <c r="I14" s="2">
-        <v>197</v>
+        <v>233</v>
       </c>
       <c r="J14" s="3">
-        <v>0.08121827411167512</v>
+        <v>0.06866952789699571</v>
       </c>
     </row>
     <row r="15" spans="1:10">
       <c r="A15" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>11</v>
@@ -985,30 +979,30 @@
         <v>34</v>
       </c>
       <c r="F15" s="3">
-        <v>0.4852941176470588</v>
+        <v>0.4676470588235294</v>
       </c>
       <c r="G15" s="3">
-        <v>-1.787556008478546</v>
+        <v>-1.544471087044477</v>
       </c>
       <c r="H15" s="2">
         <v>16</v>
       </c>
       <c r="I15" s="2">
-        <v>232</v>
+        <v>227</v>
       </c>
       <c r="J15" s="3">
-        <v>0.06896551724137931</v>
+        <v>0.07048458149779736</v>
       </c>
     </row>
     <row r="16" spans="1:10">
       <c r="A16" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C16" s="2">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D16" s="1" t="s">
         <v>35</v>
@@ -1017,56 +1011,56 @@
         <v>36</v>
       </c>
       <c r="F16" s="3">
-        <v>0.446875</v>
+        <v>0.4666666666666667</v>
       </c>
       <c r="G16" s="3">
-        <v>-1.512214299712362</v>
+        <v>-1.40296084881446</v>
       </c>
       <c r="H16" s="2">
         <v>16</v>
       </c>
       <c r="I16" s="2">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="J16" s="3">
-        <v>0.07655502392344497</v>
+        <v>0.07441860465116279</v>
       </c>
     </row>
     <row r="17" spans="1:10">
       <c r="A17" s="1" t="s">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C17" s="2">
+        <v>34</v>
+      </c>
+      <c r="D17" s="1" t="s">
         <v>35</v>
-      </c>
-      <c r="D17" s="1" t="s">
-        <v>21</v>
       </c>
       <c r="E17" s="1" t="s">
         <v>37</v>
       </c>
       <c r="F17" s="3">
-        <v>0.4428571428571428</v>
+        <v>0.4382352941176471</v>
       </c>
       <c r="G17" s="3">
-        <v>-1.875365992819716</v>
+        <v>-2.154431774498309</v>
       </c>
       <c r="H17" s="2">
         <v>16</v>
       </c>
       <c r="I17" s="2">
-        <v>227</v>
+        <v>216</v>
       </c>
       <c r="J17" s="3">
-        <v>0.07048458149779736</v>
+        <v>0.07407407407407407</v>
       </c>
     </row>
     <row r="18" spans="1:10">
       <c r="A18" s="1" t="s">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>11</v>
@@ -1075,30 +1069,30 @@
         <v>35</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>35</v>
+        <v>19</v>
       </c>
       <c r="E18" s="1" t="s">
         <v>38</v>
       </c>
       <c r="F18" s="3">
-        <v>0.44</v>
+        <v>0.4371428571428572</v>
       </c>
       <c r="G18" s="3">
-        <v>-1.686419491647547</v>
+        <v>-2.031756362681219</v>
       </c>
       <c r="H18" s="2">
         <v>16</v>
       </c>
       <c r="I18" s="2">
-        <v>225</v>
+        <v>221</v>
       </c>
       <c r="J18" s="3">
-        <v>0.07111111111111111</v>
+        <v>0.07239819004524888</v>
       </c>
     </row>
     <row r="19" spans="1:10">
       <c r="A19" s="1" t="s">
-        <v>39</v>
+        <v>14</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>11</v>
@@ -1107,62 +1101,62 @@
         <v>35</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F19" s="3">
-        <v>0.4371428571428572</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="G19" s="3">
-        <v>-2.031756362681219</v>
+        <v>-1.676996393143505</v>
       </c>
       <c r="H19" s="2">
         <v>16</v>
       </c>
       <c r="I19" s="2">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="J19" s="3">
-        <v>0.07239819004524888</v>
+        <v>0.07142857142857142</v>
       </c>
     </row>
     <row r="20" spans="1:10">
       <c r="A20" s="1" t="s">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C20" s="2">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F20" s="3">
-        <v>0.4371428571428572</v>
+        <v>0.4121212121212121</v>
       </c>
       <c r="G20" s="3">
-        <v>-2.031756362681219</v>
+        <v>-1.948657094153874</v>
       </c>
       <c r="H20" s="2">
         <v>16</v>
       </c>
       <c r="I20" s="2">
-        <v>221</v>
+        <v>206</v>
       </c>
       <c r="J20" s="3">
-        <v>0.07239819004524888</v>
+        <v>0.07766990291262135</v>
       </c>
     </row>
     <row r="21" spans="1:10">
       <c r="A21" s="1" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>11</v>
@@ -1171,10 +1165,10 @@
         <v>33</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>42</v>
+        <v>24</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="F21" s="3">
         <v>0.4121212121212121</v>
